--- a/erp-server/erp-server-oms/src/main/resources/excel/kolSampleCostTemplate.xlsx
+++ b/erp-server/erp-server-oms/src/main/resources/excel/kolSampleCostTemplate.xlsx
@@ -1051,6 +1051,11 @@
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="B2:B1048576">
+      <formula1>"物流费,订单费用,关税"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
